--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487902_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487902_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3149</v>
+        <v>4.346</v>
       </c>
       <c r="E2" t="n">
-        <v>1.54</v>
+        <v>2.2482</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7749</v>
+        <v>2.0978</v>
       </c>
       <c r="G2" t="n">
         <v>2.2285</v>
@@ -610,13 +610,13 @@
         <v>1.4568</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.8783</v>
+        <v>-0.8471</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8358</v>
+        <v>-0.1276</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.0425</v>
+        <v>-0.7195</v>
       </c>
       <c r="V2" t="n">
         <v>1.7159</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5843</v>
+        <v>2.771</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.6012</v>
+        <v>0.3213</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1855</v>
+        <v>2.4497</v>
       </c>
       <c r="G3" t="n">
         <v>3.4746</v>
@@ -688,13 +688,13 @@
         <v>2.4974</v>
       </c>
       <c r="S3" t="n">
-        <v>-2.5418</v>
+        <v>-1.355</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.2272</v>
+        <v>-0.3047</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.3145</v>
+        <v>-1.0503</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3892</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. SALL</t>
+          <t>S. SERRATO BALLETBO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1049</v>
+        <v>0.8717</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5844</v>
+        <v>0.7175</v>
       </c>
       <c r="F4" t="n">
-        <v>0.5206</v>
+        <v>0.1542</v>
       </c>
       <c r="G4" t="n">
-        <v>3.1068</v>
+        <v>2.201</v>
       </c>
       <c r="H4" t="n">
-        <v>2.697</v>
+        <v>0.1771</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4099</v>
+        <v>2.0239</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1967</v>
+        <v>2.0501</v>
       </c>
       <c r="K4" t="n">
-        <v>2.0399</v>
+        <v>-0.2922</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1568</v>
+        <v>2.3423</v>
       </c>
       <c r="M4" t="n">
-        <v>0.9102</v>
+        <v>0.1509</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6571</v>
+        <v>0.4693</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2531</v>
+        <v>-0.3184</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.4568</v>
+        <v>-1.0406</v>
       </c>
       <c r="Q4" t="n">
-        <v>-2.0812</v>
+        <v>-1.2487</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6244</v>
+        <v>0.2081</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1625</v>
+        <v>-0.5185999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5748</v>
+        <v>-0.3138</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7373</v>
+        <v>-0.2048</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.7076</v>
+        <v>0.23</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0437</v>
+        <v>0.23</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.7513</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S. SERRATO BALLETBO</t>
+          <t>P. SALL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.7543</v>
+        <v>0.4068</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7175</v>
+        <v>0.6496</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0368</v>
+        <v>-0.2428</v>
       </c>
       <c r="G5" t="n">
-        <v>2.201</v>
+        <v>3.1068</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1771</v>
+        <v>2.697</v>
       </c>
       <c r="I5" t="n">
-        <v>2.0239</v>
+        <v>0.4099</v>
       </c>
       <c r="J5" t="n">
-        <v>2.0501</v>
+        <v>2.1967</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.2922</v>
+        <v>2.0399</v>
       </c>
       <c r="L5" t="n">
-        <v>2.3423</v>
+        <v>0.1568</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1509</v>
+        <v>0.9102</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4693</v>
+        <v>0.6571</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3184</v>
+        <v>0.2531</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.0406</v>
+        <v>-1.4568</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.2487</v>
+        <v>-2.0812</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2081</v>
+        <v>0.6244</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6361</v>
+        <v>-0.5356</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.3138</v>
+        <v>-0.5096000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3223</v>
+        <v>-0.026</v>
       </c>
       <c r="V5" t="n">
-        <v>0.23</v>
+        <v>-0.7076</v>
       </c>
       <c r="W5" t="n">
-        <v>0.23</v>
+        <v>1.0437</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.7513</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. SANTOS SPENCER</t>
+          <t>A. BIRD-JELINEK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5256</v>
+        <v>0.1848</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3524</v>
+        <v>0.2224</v>
       </c>
       <c r="F6" t="n">
-        <v>0.878</v>
+        <v>-0.0376</v>
       </c>
       <c r="G6" t="n">
-        <v>2.2809</v>
+        <v>2.0618</v>
       </c>
       <c r="H6" t="n">
-        <v>2.1151</v>
+        <v>0.7294</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1657</v>
+        <v>1.3324</v>
       </c>
       <c r="J6" t="n">
-        <v>2.1259</v>
+        <v>0.6372</v>
       </c>
       <c r="K6" t="n">
-        <v>1.8908</v>
+        <v>0.0192</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2351</v>
+        <v>0.618</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1549</v>
+        <v>1.4246</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2243</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0694</v>
+        <v>0.7144</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.6649</v>
+        <v>0.4162</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.538</v>
+        <v>-0.2081</v>
       </c>
       <c r="R6" t="n">
-        <v>1.8731</v>
+        <v>0.6244</v>
       </c>
       <c r="S6" t="n">
-        <v>1.3603</v>
+        <v>-0.542</v>
       </c>
       <c r="T6" t="n">
-        <v>1.3073</v>
+        <v>-0.2067</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0529</v>
+        <v>-0.3353</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.4506</v>
+        <v>-1.7513</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.2477</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2029</v>
+        <v>-1.7513</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. BIRD-JELINEK</t>
+          <t>A. RODRIGUEZ MONTON</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1051</v>
+        <v>-0.7847</v>
       </c>
       <c r="E7" t="n">
-        <v>0.05</v>
+        <v>-1.1713</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1551</v>
+        <v>0.3866</v>
       </c>
       <c r="G7" t="n">
-        <v>2.0618</v>
+        <v>-0.2792</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7294</v>
+        <v>0.5992</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3324</v>
+        <v>-0.8784999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6372</v>
+        <v>-0.275</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0192</v>
+        <v>0.3218</v>
       </c>
       <c r="L7" t="n">
-        <v>0.618</v>
+        <v>-0.5968</v>
       </c>
       <c r="M7" t="n">
-        <v>1.4246</v>
+        <v>-0.0042</v>
       </c>
       <c r="N7" t="n">
-        <v>0.7102000000000001</v>
+        <v>0.2775</v>
       </c>
       <c r="O7" t="n">
-        <v>0.7144</v>
+        <v>-0.2817</v>
       </c>
       <c r="P7" t="n">
         <v>0.4162</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.2081</v>
+        <v>-0.4162</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6244</v>
+        <v>0.8325</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8318</v>
+        <v>-0.9217</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3791</v>
+        <v>-0.48</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4527</v>
+        <v>-0.4416</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.7513</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.7513</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ MONTON</t>
+          <t>P. SANTOS SPENCER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1038</v>
+        <v>-0.9379</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3437</v>
+        <v>-1.3168</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2398</v>
+        <v>0.3789</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.2792</v>
+        <v>2.2809</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5992</v>
+        <v>2.1151</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8784999999999999</v>
+        <v>0.1657</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.275</v>
+        <v>2.1259</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3218</v>
+        <v>1.8908</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5968</v>
+        <v>0.2351</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0042</v>
+        <v>0.1549</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2775</v>
+        <v>0.2243</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2817</v>
+        <v>-0.0694</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4162</v>
+        <v>-1.6649</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.4162</v>
+        <v>-3.538</v>
       </c>
       <c r="R8" t="n">
-        <v>0.8325</v>
+        <v>1.8731</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.2409</v>
+        <v>-0.1032</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6524</v>
+        <v>0.3429</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5884</v>
+        <v>-0.4462</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.4506</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.2477</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.2029</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2454</v>
+        <v>-1.9647</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4143</v>
+        <v>-2.4859</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1689</v>
+        <v>0.5212</v>
       </c>
       <c r="G9" t="n">
         <v>0.3025</v>
@@ -1156,13 +1156,13 @@
         <v>1.2487</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6602</v>
+        <v>-0.059</v>
       </c>
       <c r="T9" t="n">
-        <v>1.4378</v>
+        <v>0.3663</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7776</v>
+        <v>-0.4253</v>
       </c>
       <c r="V9" t="n">
         <v>-1.1675</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.3386</v>
+        <v>-3.8964</v>
       </c>
       <c r="E10" t="n">
         <v>-4.1517</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.2552</v>
       </c>
       <c r="G10" t="n">
         <v>-1.137</v>
@@ -1234,13 +1234,13 @@
         <v>1.6649</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1657</v>
+        <v>-0.3921</v>
       </c>
       <c r="T10" t="n">
         <v>-0.0562</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2219</v>
+        <v>-0.3359</v>
       </c>
       <c r="V10" t="n">
         <v>-1.3267</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.3152</v>
+        <v>-4.4946</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.4521</v>
+        <v>-4.1306</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.8631</v>
+        <v>-0.364</v>
       </c>
       <c r="G11" t="n">
         <v>0.0272</v>
@@ -1312,13 +1312,13 @@
         <v>2.4974</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.0375</v>
+        <v>-1.2169</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.37</v>
+        <v>-0.0485</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.6675</v>
+        <v>-1.1684</v>
       </c>
       <c r="V11" t="n">
         <v>-2.2643</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.824099999999999</v>
+        <v>-3.497999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-9.423499999999999</v>
+        <v>-9.097300000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>5.599299999999999</v>
+        <v>5.599200000000001</v>
       </c>
       <c r="G12" t="n">
         <v>14.2671</v>
@@ -1390,13 +1390,13 @@
         <v>13.5277</v>
       </c>
       <c r="S12" t="n">
-        <v>-6.8177</v>
+        <v>-6.491199999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.6642</v>
+        <v>-1.3379</v>
       </c>
       <c r="U12" t="n">
-        <v>-5.1534</v>
+        <v>-5.1533</v>
       </c>
       <c r="V12" t="n">
         <v>-7.1113</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.6426</v>
+        <v>4.2934</v>
       </c>
       <c r="E13" t="n">
-        <v>4.7499</v>
+        <v>4.9643</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.1073</v>
+        <v>-0.6709000000000001</v>
       </c>
       <c r="G13" t="n">
         <v>3.1295</v>
@@ -1468,13 +1468,13 @@
         <v>1.8731</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.5822000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0215</v>
+        <v>0.2358</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.09</v>
+        <v>0.3464</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2914</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. MENDIOLA DIEZ</t>
+          <t>V. MORENO MARTIN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.5963</v>
+        <v>2.4564</v>
       </c>
       <c r="E14" t="n">
-        <v>2.2556</v>
+        <v>-0.3579</v>
       </c>
       <c r="F14" t="n">
-        <v>1.3407</v>
+        <v>2.8143</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.6655</v>
+        <v>-1.5737</v>
       </c>
       <c r="H14" t="n">
-        <v>0.1509</v>
+        <v>-0.5181</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8164</v>
+        <v>-1.0556</v>
       </c>
       <c r="J14" t="n">
-        <v>0.7307</v>
+        <v>-1.9369</v>
       </c>
       <c r="K14" t="n">
-        <v>0.7307</v>
+        <v>-0.4118</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>-1.5251</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.3962</v>
+        <v>0.3632</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5798</v>
+        <v>-0.1063</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.8164</v>
+        <v>0.4695</v>
       </c>
       <c r="P14" t="n">
-        <v>1.4568</v>
+        <v>1.0406</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R14" t="n">
-        <v>1.4568</v>
+        <v>2.0812</v>
       </c>
       <c r="S14" t="n">
-        <v>2.575</v>
+        <v>1.3621</v>
       </c>
       <c r="T14" t="n">
-        <v>1.295</v>
+        <v>0.9921</v>
       </c>
       <c r="U14" t="n">
-        <v>1.2801</v>
+        <v>0.37</v>
       </c>
       <c r="V14" t="n">
-        <v>0.23</v>
+        <v>1.6275</v>
       </c>
       <c r="W14" t="n">
-        <v>0.23</v>
+        <v>1.6275</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>V. MORENO MARTIN</t>
+          <t>S. MENDIOLA DIEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.8493</v>
+        <v>2.259</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1778</v>
+        <v>1.5055</v>
       </c>
       <c r="F15" t="n">
-        <v>2.6714</v>
+        <v>0.7534999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.5737</v>
+        <v>-0.6655</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.5181</v>
+        <v>0.1509</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.0556</v>
+        <v>-0.8164</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.9369</v>
+        <v>0.7307</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.4118</v>
+        <v>0.7307</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.5251</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.3632</v>
+        <v>-1.3962</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1063</v>
+        <v>-0.5798</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4695</v>
+        <v>-0.8164</v>
       </c>
       <c r="P15" t="n">
-        <v>1.0406</v>
+        <v>1.4568</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.0812</v>
+        <v>1.4568</v>
       </c>
       <c r="S15" t="n">
-        <v>1.755</v>
+        <v>1.2378</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5279</v>
+        <v>0.5449000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2271</v>
+        <v>0.6929</v>
       </c>
       <c r="V15" t="n">
-        <v>1.6275</v>
+        <v>0.23</v>
       </c>
       <c r="W15" t="n">
-        <v>1.6275</v>
+        <v>0.23</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5526</v>
+        <v>1.3194</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2344</v>
+        <v>0.7702</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3182</v>
+        <v>0.5491</v>
       </c>
       <c r="G16" t="n">
         <v>-3.0095</v>
@@ -1702,13 +1702,13 @@
         <v>2.4974</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3327</v>
+        <v>0.434</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0438</v>
+        <v>0.492</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.289</v>
+        <v>-0.058</v>
       </c>
       <c r="V16" t="n">
         <v>1.3975</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0437</v>
+        <v>0.9041</v>
       </c>
       <c r="E17" t="n">
-        <v>-3.0275</v>
+        <v>-2.2774</v>
       </c>
       <c r="F17" t="n">
-        <v>2.9838</v>
+        <v>3.1815</v>
       </c>
       <c r="G17" t="n">
         <v>-1.8946</v>
@@ -1780,13 +1780,13 @@
         <v>2.2893</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1246</v>
+        <v>1.0724</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2271</v>
+        <v>0.523</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3517</v>
+        <v>0.5494</v>
       </c>
       <c r="V17" t="n">
         <v>0.4776</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>F. SIERRA GALA</t>
+          <t>S. KOCIC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1888</v>
+        <v>0.205</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.2724</v>
+        <v>-1.4918</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0836</v>
+        <v>1.6968</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.9221</v>
+        <v>-0.6931</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.1473</v>
+        <v>-0.9510999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7748</v>
+        <v>0.258</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.6322</v>
+        <v>-0.6441</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.2819</v>
+        <v>-1.1837</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.3504</v>
+        <v>0.5396</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7102000000000001</v>
+        <v>-0.0491</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1346</v>
+        <v>0.2326</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5756</v>
+        <v>-0.2817</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.4568</v>
+        <v>-2.9137</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.1218</v>
+        <v>-4.1624</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6649</v>
+        <v>1.2487</v>
       </c>
       <c r="S18" t="n">
-        <v>2.1901</v>
+        <v>0.893</v>
       </c>
       <c r="T18" t="n">
-        <v>2.0217</v>
+        <v>0.3958</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1684</v>
+        <v>0.4972</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>2.9188</v>
       </c>
       <c r="W18" t="n">
-        <v>0.4599</v>
+        <v>2.9188</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.4599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. KOCIC</t>
+          <t>I. ALVAREZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.4942</v>
+        <v>-1.1234</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.8133</v>
+        <v>-0.4205</v>
       </c>
       <c r="F19" t="n">
-        <v>1.3191</v>
+        <v>-0.703</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6931</v>
+        <v>-2.4644</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.9510999999999999</v>
+        <v>-0.0788</v>
       </c>
       <c r="I19" t="n">
-        <v>0.258</v>
+        <v>-2.3856</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6441</v>
+        <v>-0.411</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.1837</v>
+        <v>0.9786</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5396</v>
+        <v>-1.3896</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0491</v>
+        <v>-2.0535</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2326</v>
+        <v>-1.0574</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2817</v>
+        <v>-0.996</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.9137</v>
+        <v>1.2487</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.1624</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>1.2487</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1937</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0743</v>
+        <v>-0.0095</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1194</v>
+        <v>0.1018</v>
       </c>
       <c r="V19" t="n">
-        <v>2.9188</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.9188</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>V. STEVANIC</t>
+          <t>F. SIERRA GALA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.6065</v>
+        <v>-1.2055</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1987</v>
+        <v>-3.3439</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4079</v>
+        <v>2.1384</v>
       </c>
       <c r="G20" t="n">
-        <v>-4.5022</v>
+        <v>-0.9221</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.1558</v>
+        <v>-0.1473</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.3464</v>
+        <v>-0.7748</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.2079</v>
+        <v>-1.6322</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.8575</v>
+        <v>-0.2819</v>
       </c>
       <c r="L20" t="n">
         <v>-1.3504</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.2943</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.2983</v>
+        <v>0.1346</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.996</v>
+        <v>0.5756</v>
       </c>
       <c r="P20" t="n">
-        <v>1.4568</v>
+        <v>-1.4568</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-3.1218</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4568</v>
+        <v>1.6649</v>
       </c>
       <c r="S20" t="n">
-        <v>2.0851</v>
+        <v>1.1733</v>
       </c>
       <c r="T20" t="n">
-        <v>1.4254</v>
+        <v>0.9502</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6596</v>
+        <v>0.2232</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3538</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.5838</v>
+        <v>0.4599</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.23</v>
+        <v>-0.4599</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. ALVAREZ FERNANDEZ</t>
+          <t>V. STEVANIC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.056</v>
+        <v>-1.728</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0634</v>
+        <v>-1.0559</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.9926</v>
+        <v>-0.6721</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.4644</v>
+        <v>-4.5022</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0788</v>
+        <v>-2.1558</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.3856</v>
+        <v>-2.3464</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.411</v>
+        <v>-2.2079</v>
       </c>
       <c r="K21" t="n">
-        <v>0.9786</v>
+        <v>-0.8575</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.3896</v>
+        <v>-1.3504</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.0535</v>
+        <v>-2.2943</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.0574</v>
+        <v>-1.2983</v>
       </c>
       <c r="O21" t="n">
         <v>-0.996</v>
       </c>
       <c r="P21" t="n">
-        <v>1.2487</v>
+        <v>1.4568</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.2487</v>
+        <v>1.4568</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8403</v>
+        <v>0.9636</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6524</v>
+        <v>0.5682</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1879</v>
+        <v>0.3954</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.3538</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.5838</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.4275</v>
+        <v>-2.1274</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.642</v>
+        <v>-3.8919</v>
       </c>
       <c r="F22" t="n">
-        <v>1.2145</v>
+        <v>1.7645</v>
       </c>
       <c r="G22" t="n">
         <v>-1.6712</v>
@@ -2170,13 +2170,13 @@
         <v>1.8731</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8643999999999999</v>
+        <v>0.4356</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2891</v>
+        <v>0.461</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5754</v>
+        <v>-0.0254</v>
       </c>
       <c r="V22" t="n">
         <v>1.3975</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>3.824099999999999</v>
+        <v>5.253000000000002</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.5996</v>
+        <v>-5.5993</v>
       </c>
       <c r="F23" t="n">
-        <v>9.423500000000001</v>
+        <v>10.8521</v>
       </c>
       <c r="G23" t="n">
         <v>-14.2668</v>
@@ -2218,7 +2218,7 @@
         <v>-10.0012</v>
       </c>
       <c r="I23" t="n">
-        <v>-4.2658</v>
+        <v>-4.265799999999999</v>
       </c>
       <c r="J23" t="n">
         <v>-6.530000000000001</v>
@@ -2248,16 +2248,16 @@
         <v>17.69</v>
       </c>
       <c r="S23" t="n">
-        <v>6.817600000000001</v>
+        <v>8.246300000000002</v>
       </c>
       <c r="T23" t="n">
-        <v>5.1534</v>
+        <v>5.1535</v>
       </c>
       <c r="U23" t="n">
-        <v>1.664</v>
+        <v>3.0929</v>
       </c>
       <c r="V23" t="n">
-        <v>7.1113</v>
+        <v>7.111299999999999</v>
       </c>
       <c r="W23" t="n">
         <v>9.3049</v>
